--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -3209,14 +3209,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -5691,7 +5684,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Done</v>
@@ -5771,7 +5764,7 @@
         <v>m.hqporner.com</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Done</v>
@@ -8331,7 +8324,7 @@
         <v>bdsmmansion.com</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Done</v>
@@ -8651,7 +8644,7 @@
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Done</v>
@@ -9211,7 +9204,7 @@
         <v>hcbdsm.com</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Done</v>
@@ -10971,7 +10964,7 @@
         <v>bdsmmansion.com</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="str">
         <f t="shared" si="2"/>
         <v>Done</v>
@@ -12136,13 +12129,13 @@
     <sortCondition descending="1" ref="I1:I205"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="M1:T215">
-    <cfRule type="expression" dxfId="1" priority="10">
+  <conditionalFormatting sqref="A1:L215">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:L215">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="M1:T215">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
